--- a/attachments/Allocations_Multiple.xlsx
+++ b/attachments/Allocations_Multiple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Apps\RJF.TradeAllocBridge\src\RJF.TradeAllocBridge.CLI\bin\Debug\net8.0-windows\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{610ACC5B-89E7-4177-90A6-AD87DE24CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D8A66C0-02A0-4CEA-9530-766B41E6B987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{619E463A-8D35-493B-A9CF-06F38D4871CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{3198B14B-3073-44B6-89DF-2DC0BF37C1CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Allocations_Multiple" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="29">
   <si>
     <t xml:space="preserve">Cust </t>
   </si>
@@ -28,6 +28,21 @@
     <t>Broker</t>
   </si>
   <si>
+    <t xml:space="preserve">Side </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Symbol </t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExecutedQty  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AvgPrc </t>
+  </si>
+  <si>
     <t xml:space="preserve">Settle </t>
   </si>
   <si>
@@ -43,6 +58,9 @@
     <t xml:space="preserve">TotalFees  </t>
   </si>
   <si>
+    <t xml:space="preserve">TradeDate </t>
+  </si>
+  <si>
     <t xml:space="preserve">SettleDate </t>
   </si>
   <si>
@@ -61,6 +79,9 @@
     <t>FIS</t>
   </si>
   <si>
+    <t>31620M106</t>
+  </si>
+  <si>
     <t>USD</t>
   </si>
   <si>
@@ -79,9 +100,6 @@
     <t>TCBK</t>
   </si>
   <si>
-    <t>31620M106</t>
-  </si>
-  <si>
     <t>31620M107</t>
   </si>
   <si>
@@ -89,31 +107,13 @@
   </si>
   <si>
     <t>31620M109</t>
-  </si>
-  <si>
-    <t>ExecutedQty</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>Side</t>
-  </si>
-  <si>
-    <t>AvgPrc</t>
-  </si>
-  <si>
-    <t>TradeDate</t>
-  </si>
-  <si>
-    <t>Order</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,12 +244,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -596,12 +590,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -976,17 +969,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844F7F59-E9C6-4A76-90C6-EE6F204EE0B8}">
-  <dimension ref="A1:O18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E39681-4401-4FAB-AF0F-4A1BFBB0ED87}">
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -996,57 +981,57 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -1058,7 +1043,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
         <v>601245.81000000006</v>
@@ -1079,21 +1064,21 @@
         <v>45960</v>
       </c>
       <c r="O2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -1105,7 +1090,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
         <v>756021.96</v>
@@ -1126,21 +1111,21 @@
         <v>45960</v>
       </c>
       <c r="O3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1152,7 +1137,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2">
         <v>111080.42</v>
@@ -1173,21 +1158,21 @@
         <v>45960</v>
       </c>
       <c r="O4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -1199,7 +1184,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
         <v>65911.81</v>
@@ -1220,21 +1205,21 @@
         <v>45960</v>
       </c>
       <c r="O5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -1246,7 +1231,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
         <v>593244.66</v>
@@ -1267,21 +1252,21 @@
         <v>45960</v>
       </c>
       <c r="O6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -1293,7 +1278,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
         <v>745110.45</v>
@@ -1314,21 +1299,21 @@
         <v>45960</v>
       </c>
       <c r="O7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -1340,7 +1325,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
         <v>109270.77</v>
@@ -1361,21 +1346,21 @@
         <v>45960</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -1387,7 +1372,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2">
         <v>64981.62</v>
@@ -1408,21 +1393,21 @@
         <v>45960</v>
       </c>
       <c r="O9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1434,7 +1419,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2">
         <v>593858.47</v>
@@ -1455,21 +1440,21 @@
         <v>45960</v>
       </c>
       <c r="O10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -1481,7 +1466,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
         <v>748149.99</v>
@@ -1502,21 +1487,21 @@
         <v>45960</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -1528,7 +1513,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
         <v>110104.18</v>
@@ -1549,21 +1534,21 @@
         <v>45960</v>
       </c>
       <c r="O12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -1575,7 +1560,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
         <v>65309.86</v>
@@ -1596,23 +1581,23 @@
         <v>45960</v>
       </c>
       <c r="O13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4">
+        <v>25</v>
+      </c>
+      <c r="E14">
         <v>896095106</v>
       </c>
       <c r="F14" s="1">
@@ -1622,7 +1607,7 @@
         <v>44.499600000000001</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
         <v>53399.519999999997</v>
@@ -1643,21 +1628,21 @@
         <v>45960</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -1669,7 +1654,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I15" s="2">
         <v>287476.15000000002</v>
@@ -1690,24 +1675,24 @@
         <v>45960</v>
       </c>
       <c r="O15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1">
         <v>5943</v>
@@ -1716,7 +1701,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
         <v>362194.35</v>
@@ -1737,24 +1722,24 @@
         <v>45960</v>
       </c>
       <c r="O16" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F17">
         <v>873</v>
@@ -1763,7 +1748,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2">
         <v>53204.72</v>
@@ -1784,24 +1769,24 @@
         <v>45960</v>
       </c>
       <c r="O17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>519</v>
@@ -1810,7 +1795,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2">
         <v>31630.3</v>
@@ -1831,11 +1816,57 @@
         <v>45960</v>
       </c>
       <c r="O18" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>896095106</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G19">
+        <v>44.499600000000001</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="2">
+        <v>53399.519999999997</v>
+      </c>
+      <c r="J19" s="2">
+        <v>53435.519999999997</v>
+      </c>
+      <c r="K19">
+        <v>36</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>45959</v>
+      </c>
+      <c r="N19" s="3">
+        <v>45960</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/attachments/Allocations_Multiple.xlsx
+++ b/attachments/Allocations_Multiple.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Apps\RJF.TradeAllocBridge\src\RJF.TradeAllocBridge.CLI\bin\Debug\net8.0-windows\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakme\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D8A66C0-02A0-4CEA-9530-766B41E6B987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341EF895-3610-4B49-B6DA-FF8CD2A87492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{3198B14B-3073-44B6-89DF-2DC0BF37C1CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{619E463A-8D35-493B-A9CF-06F38D4871CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Allocations_Multiple" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="25">
   <si>
     <t xml:space="preserve">Cust </t>
   </si>
@@ -28,21 +28,6 @@
     <t>Broker</t>
   </si>
   <si>
-    <t xml:space="preserve">Side </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Symbol </t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExecutedQty  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvgPrc </t>
-  </si>
-  <si>
     <t xml:space="preserve">Settle </t>
   </si>
   <si>
@@ -58,9 +43,6 @@
     <t xml:space="preserve">TotalFees  </t>
   </si>
   <si>
-    <t xml:space="preserve">TradeDate </t>
-  </si>
-  <si>
     <t xml:space="preserve">SettleDate </t>
   </si>
   <si>
@@ -79,9 +61,6 @@
     <t>FIS</t>
   </si>
   <si>
-    <t>31620M106</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -100,20 +79,29 @@
     <t>TCBK</t>
   </si>
   <si>
-    <t>31620M107</t>
-  </si>
-  <si>
-    <t>31620M108</t>
-  </si>
-  <si>
-    <t>31620M109</t>
+    <t>ExecutedQty</t>
+  </si>
+  <si>
+    <t>AvgPrc</t>
+  </si>
+  <si>
+    <t>TradeDate</t>
+  </si>
+  <si>
+    <t>SIDE</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Sell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +232,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -969,11 +963,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E39681-4401-4FAB-AF0F-4A1BFBB0ED87}">
-  <dimension ref="A1:O19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844F7F59-E9C6-4A76-90C6-EE6F204EE0B8}">
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,892 +982,836 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="E2" s="1">
+        <v>9797</v>
+      </c>
+      <c r="F2">
+        <v>61.370399999999997</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="H2" s="2">
+        <v>601245.81000000006</v>
+      </c>
+      <c r="I2" s="2">
+        <v>601539.72</v>
+      </c>
+      <c r="J2">
+        <v>293.91000000000003</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M2" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <v>12319</v>
+      </c>
+      <c r="F3">
+        <v>61.370399999999997</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2">
+        <v>756021.96</v>
+      </c>
+      <c r="I3" s="2">
+        <v>756391.53</v>
+      </c>
+      <c r="J3">
+        <v>369.57</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M3" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1810</v>
+      </c>
+      <c r="F4">
+        <v>61.370399999999997</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2">
+        <v>111080.42</v>
+      </c>
+      <c r="I4" s="2">
+        <v>111134.72</v>
+      </c>
+      <c r="J4">
+        <v>54.3</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M4" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1074</v>
+      </c>
+      <c r="F5">
+        <v>61.370399999999997</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2">
+        <v>65911.81</v>
+      </c>
+      <c r="I5" s="2">
+        <v>65944.03</v>
+      </c>
+      <c r="J5">
+        <v>32.22</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M5" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9805</v>
+      </c>
+      <c r="F6">
+        <v>60.504300000000001</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2">
+        <v>593244.66</v>
+      </c>
+      <c r="I6" s="2">
+        <v>593538.81000000006</v>
+      </c>
+      <c r="J6">
+        <v>294.14999999999998</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M6" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1">
+        <v>12315</v>
+      </c>
+      <c r="F7">
+        <v>60.504300000000001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2">
+        <v>745110.45</v>
+      </c>
+      <c r="I7" s="2">
+        <v>745479.9</v>
+      </c>
+      <c r="J7">
+        <v>369.45</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M7" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1806</v>
+      </c>
+      <c r="F8">
+        <v>60.504300000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2">
+        <v>109270.77</v>
+      </c>
+      <c r="I8" s="2">
+        <v>109324.95</v>
+      </c>
+      <c r="J8">
+        <v>54.18</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M8" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1074</v>
+      </c>
+      <c r="F9">
+        <v>60.504300000000001</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="2">
+        <v>64981.62</v>
+      </c>
+      <c r="I9" s="2">
+        <v>65013.84</v>
+      </c>
+      <c r="J9">
+        <v>32.22</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M9" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1">
+        <v>9784</v>
+      </c>
+      <c r="F10">
+        <v>60.696899999999999</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2">
+        <v>593858.47</v>
+      </c>
+      <c r="I10" s="2">
+        <v>594151.99</v>
+      </c>
+      <c r="J10">
+        <v>293.52</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M10" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1">
+        <v>12326</v>
+      </c>
+      <c r="F11">
+        <v>60.696899999999999</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2">
+        <v>748149.99</v>
+      </c>
+      <c r="I11" s="2">
+        <v>748519.77</v>
+      </c>
+      <c r="J11">
+        <v>369.78</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M11" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1814</v>
+      </c>
+      <c r="F12">
+        <v>60.696899999999999</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2">
+        <v>110104.18</v>
+      </c>
+      <c r="I12" s="2">
+        <v>110158.6</v>
+      </c>
+      <c r="J12">
+        <v>54.42</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M12" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1076</v>
+      </c>
+      <c r="F13">
+        <v>60.696899999999999</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2">
+        <v>65309.86</v>
+      </c>
+      <c r="I13" s="2">
+        <v>65342.14</v>
+      </c>
+      <c r="J13">
+        <v>32.28</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M13" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1">
-        <v>9797</v>
-      </c>
-      <c r="G2">
-        <v>61.370399999999997</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="2">
-        <v>601245.81000000006</v>
-      </c>
-      <c r="J2" s="2">
-        <v>601539.72</v>
-      </c>
-      <c r="K2">
-        <v>293.91000000000003</v>
-      </c>
-      <c r="L2">
+      <c r="E14" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F14">
+        <v>44.499600000000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2">
+        <v>53399.519999999997</v>
+      </c>
+      <c r="I14" s="2">
+        <v>53435.519999999997</v>
+      </c>
+      <c r="J14">
+        <v>36</v>
+      </c>
+      <c r="K14">
         <v>0</v>
       </c>
-      <c r="M2" s="3">
+      <c r="L14" s="3">
         <v>45959</v>
       </c>
-      <c r="N2" s="3">
+      <c r="M14" s="3">
         <v>45960</v>
       </c>
-      <c r="O2" t="s">
-        <v>21</v>
+      <c r="N14" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4717</v>
+      </c>
+      <c r="F15">
+        <v>60.944699999999997</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2">
+        <v>287476.15000000002</v>
+      </c>
+      <c r="I15" s="2">
+        <v>287617.65999999997</v>
+      </c>
+      <c r="J15">
+        <v>141.51</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M15" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5943</v>
+      </c>
+      <c r="F16">
+        <v>60.944699999999997</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2">
+        <v>362194.35</v>
+      </c>
+      <c r="I16" s="2">
+        <v>362372.64</v>
+      </c>
+      <c r="J16">
+        <v>178.29</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M16" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>873</v>
+      </c>
+      <c r="F17">
+        <v>60.944699999999997</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2">
+        <v>53204.72</v>
+      </c>
+      <c r="I17" s="2">
+        <v>53230.91</v>
+      </c>
+      <c r="J17">
+        <v>26.19</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M17" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18">
+        <v>519</v>
+      </c>
+      <c r="F18">
+        <v>60.944699999999997</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2">
+        <v>31630.3</v>
+      </c>
+      <c r="I18" s="2">
+        <v>31645.87</v>
+      </c>
+      <c r="J18">
+        <v>15.57</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>45959</v>
+      </c>
+      <c r="M18" s="3">
+        <v>45960</v>
+      </c>
+      <c r="N18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1">
-        <v>12319</v>
-      </c>
-      <c r="G3">
-        <v>61.370399999999997</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2">
-        <v>756021.96</v>
-      </c>
-      <c r="J3" s="2">
-        <v>756391.53</v>
-      </c>
-      <c r="K3">
-        <v>369.57</v>
-      </c>
-      <c r="L3">
+      <c r="E19" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F19">
+        <v>44.499600000000001</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2">
+        <v>53399.519999999997</v>
+      </c>
+      <c r="I19" s="2">
+        <v>53435.519999999997</v>
+      </c>
+      <c r="J19">
+        <v>36</v>
+      </c>
+      <c r="K19">
         <v>0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="L19" s="3">
         <v>45959</v>
       </c>
-      <c r="N3" s="3">
+      <c r="M19" s="3">
         <v>45960</v>
       </c>
-      <c r="O3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1810</v>
-      </c>
-      <c r="G4">
-        <v>61.370399999999997</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2">
-        <v>111080.42</v>
-      </c>
-      <c r="J4" s="2">
-        <v>111134.72</v>
-      </c>
-      <c r="K4">
-        <v>54.3</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N4" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1074</v>
-      </c>
-      <c r="G5">
-        <v>61.370399999999997</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2">
-        <v>65911.81</v>
-      </c>
-      <c r="J5" s="2">
-        <v>65944.03</v>
-      </c>
-      <c r="K5">
-        <v>32.22</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N5" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1">
-        <v>9805</v>
-      </c>
-      <c r="G6">
-        <v>60.504300000000001</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2">
-        <v>593244.66</v>
-      </c>
-      <c r="J6" s="2">
-        <v>593538.81000000006</v>
-      </c>
-      <c r="K6">
-        <v>294.14999999999998</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N6" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1">
-        <v>12315</v>
-      </c>
-      <c r="G7">
-        <v>60.504300000000001</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="2">
-        <v>745110.45</v>
-      </c>
-      <c r="J7" s="2">
-        <v>745479.9</v>
-      </c>
-      <c r="K7">
-        <v>369.45</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N7" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1806</v>
-      </c>
-      <c r="G8">
-        <v>60.504300000000001</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="2">
-        <v>109270.77</v>
-      </c>
-      <c r="J8" s="2">
-        <v>109324.95</v>
-      </c>
-      <c r="K8">
-        <v>54.18</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N8" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1074</v>
-      </c>
-      <c r="G9">
-        <v>60.504300000000001</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2">
-        <v>64981.62</v>
-      </c>
-      <c r="J9" s="2">
-        <v>65013.84</v>
-      </c>
-      <c r="K9">
-        <v>32.22</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N9" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="1">
-        <v>9784</v>
-      </c>
-      <c r="G10">
-        <v>60.696899999999999</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="2">
-        <v>593858.47</v>
-      </c>
-      <c r="J10" s="2">
-        <v>594151.99</v>
-      </c>
-      <c r="K10">
-        <v>293.52</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N10" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="1">
-        <v>12326</v>
-      </c>
-      <c r="G11">
-        <v>60.696899999999999</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="2">
-        <v>748149.99</v>
-      </c>
-      <c r="J11" s="2">
-        <v>748519.77</v>
-      </c>
-      <c r="K11">
-        <v>369.78</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N11" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1814</v>
-      </c>
-      <c r="G12">
-        <v>60.696899999999999</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="2">
-        <v>110104.18</v>
-      </c>
-      <c r="J12" s="2">
-        <v>110158.6</v>
-      </c>
-      <c r="K12">
-        <v>54.42</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N12" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1076</v>
-      </c>
-      <c r="G13">
-        <v>60.696899999999999</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="2">
-        <v>65309.86</v>
-      </c>
-      <c r="J13" s="2">
-        <v>65342.14</v>
-      </c>
-      <c r="K13">
-        <v>32.28</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N13" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14">
-        <v>896095106</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1200</v>
-      </c>
-      <c r="G14">
-        <v>44.499600000000001</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="2">
-        <v>53399.519999999997</v>
-      </c>
-      <c r="J14" s="2">
-        <v>53435.519999999997</v>
-      </c>
-      <c r="K14">
-        <v>36</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N14" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4717</v>
-      </c>
-      <c r="G15">
-        <v>60.944699999999997</v>
-      </c>
-      <c r="H15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="2">
-        <v>287476.15000000002</v>
-      </c>
-      <c r="J15" s="2">
-        <v>287617.65999999997</v>
-      </c>
-      <c r="K15">
-        <v>141.51</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N15" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5943</v>
-      </c>
-      <c r="G16">
-        <v>60.944699999999997</v>
-      </c>
-      <c r="H16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="2">
-        <v>362194.35</v>
-      </c>
-      <c r="J16" s="2">
-        <v>362372.64</v>
-      </c>
-      <c r="K16">
-        <v>178.29</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N16" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17">
-        <v>873</v>
-      </c>
-      <c r="G17">
-        <v>60.944699999999997</v>
-      </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="2">
-        <v>53204.72</v>
-      </c>
-      <c r="J17" s="2">
-        <v>53230.91</v>
-      </c>
-      <c r="K17">
-        <v>26.19</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N17" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>519</v>
-      </c>
-      <c r="G18">
-        <v>60.944699999999997</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="2">
-        <v>31630.3</v>
-      </c>
-      <c r="J18" s="2">
-        <v>31645.87</v>
-      </c>
-      <c r="K18">
-        <v>15.57</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N18" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19">
-        <v>896095106</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1200</v>
-      </c>
-      <c r="G19">
-        <v>44.499600000000001</v>
-      </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="2">
-        <v>53399.519999999997</v>
-      </c>
-      <c r="J19" s="2">
-        <v>53435.519999999997</v>
-      </c>
-      <c r="K19">
-        <v>36</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>45959</v>
-      </c>
-      <c r="N19" s="3">
-        <v>45960</v>
-      </c>
-      <c r="O19" t="s">
-        <v>21</v>
+      <c r="N19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/attachments/Allocations_Multiple.xlsx
+++ b/attachments/Allocations_Multiple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zakme\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Apps\FixFlow.TradeAllocBridge\attachments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341EF895-3610-4B49-B6DA-FF8CD2A87492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C5C32D-07D0-4C87-B354-8E8FB5B5A9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{619E463A-8D35-493B-A9CF-06F38D4871CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{619E463A-8D35-493B-A9CF-06F38D4871CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Allocations_Multiple" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="24">
   <si>
     <t xml:space="preserve">Cust </t>
   </si>
@@ -46,15 +46,9 @@
     <t xml:space="preserve">SettleDate </t>
   </si>
   <si>
-    <t>Route</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
-    <t>RAJA</t>
-  </si>
-  <si>
     <t>Buy</t>
   </si>
   <si>
@@ -64,9 +58,6 @@
     <t>USD</t>
   </si>
   <si>
-    <t>RAJA-CARE-US</t>
-  </si>
-  <si>
     <t>MSCO</t>
   </si>
   <si>
@@ -95,6 +86,12 @@
   </si>
   <si>
     <t>Sell</t>
+  </si>
+  <si>
+    <t>BROK</t>
+  </si>
+  <si>
+    <t>BOFA</t>
   </si>
 </sst>
 </file>
@@ -964,17 +961,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{844F7F59-E9C6-4A76-90C6-EE6F204EE0B8}">
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" customWidth="1"/>
-    <col min="13" max="13" width="11.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.89453125" customWidth="1"/>
+    <col min="8" max="8" width="12.89453125" customWidth="1"/>
+    <col min="9" max="9" width="13.5234375" customWidth="1"/>
+    <col min="12" max="12" width="11.1015625" customWidth="1"/>
+    <col min="13" max="13" width="11.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -982,16 +979,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -1009,27 +1006,24 @@
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
       </c>
       <c r="E2" s="1">
         <v>9797</v>
@@ -1038,7 +1032,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2">
         <v>601245.81000000006</v>
@@ -1058,22 +1052,19 @@
       <c r="M2" s="3">
         <v>45960</v>
       </c>
-      <c r="N2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="1">
         <v>12319</v>
@@ -1082,7 +1073,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2">
         <v>756021.96</v>
@@ -1102,22 +1093,19 @@
       <c r="M3" s="3">
         <v>45960</v>
       </c>
-      <c r="N3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
       <c r="E4" s="1">
         <v>1810</v>
@@ -1126,7 +1114,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2">
         <v>111080.42</v>
@@ -1146,22 +1134,19 @@
       <c r="M4" s="3">
         <v>45960</v>
       </c>
-      <c r="N4" t="s">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
       </c>
       <c r="E5" s="1">
         <v>1074</v>
@@ -1170,7 +1155,7 @@
         <v>61.370399999999997</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2">
         <v>65911.81</v>
@@ -1190,22 +1175,19 @@
       <c r="M5" s="3">
         <v>45960</v>
       </c>
-      <c r="N5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>9805</v>
@@ -1214,7 +1196,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2">
         <v>593244.66</v>
@@ -1234,22 +1216,19 @@
       <c r="M6" s="3">
         <v>45960</v>
       </c>
-      <c r="N6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
       </c>
       <c r="E7" s="1">
         <v>12315</v>
@@ -1258,7 +1237,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2">
         <v>745110.45</v>
@@ -1278,22 +1257,19 @@
       <c r="M7" s="3">
         <v>45960</v>
       </c>
-      <c r="N7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
       </c>
       <c r="E8" s="1">
         <v>1806</v>
@@ -1302,7 +1278,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2">
         <v>109270.77</v>
@@ -1322,22 +1298,19 @@
       <c r="M8" s="3">
         <v>45960</v>
       </c>
-      <c r="N8" t="s">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
       </c>
       <c r="E9" s="1">
         <v>1074</v>
@@ -1346,7 +1319,7 @@
         <v>60.504300000000001</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2">
         <v>64981.62</v>
@@ -1366,22 +1339,19 @@
       <c r="M9" s="3">
         <v>45960</v>
       </c>
-      <c r="N9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
       </c>
       <c r="E10" s="1">
         <v>9784</v>
@@ -1390,7 +1360,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2">
         <v>593858.47</v>
@@ -1410,22 +1380,19 @@
       <c r="M10" s="3">
         <v>45960</v>
       </c>
-      <c r="N10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
       </c>
       <c r="E11" s="1">
         <v>12326</v>
@@ -1434,7 +1401,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2">
         <v>748149.99</v>
@@ -1454,22 +1421,19 @@
       <c r="M11" s="3">
         <v>45960</v>
       </c>
-      <c r="N11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
       </c>
       <c r="E12" s="1">
         <v>1814</v>
@@ -1478,7 +1442,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2">
         <v>110104.18</v>
@@ -1498,22 +1462,19 @@
       <c r="M12" s="3">
         <v>45960</v>
       </c>
-      <c r="N12" t="s">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
       <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
         <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
       </c>
       <c r="E13" s="1">
         <v>1076</v>
@@ -1522,7 +1483,7 @@
         <v>60.696899999999999</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2">
         <v>65309.86</v>
@@ -1542,22 +1503,19 @@
       <c r="M13" s="3">
         <v>45960</v>
       </c>
-      <c r="N13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
       </c>
       <c r="E14" s="1">
         <v>1200</v>
@@ -1566,7 +1524,7 @@
         <v>44.499600000000001</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2">
         <v>53399.519999999997</v>
@@ -1586,22 +1544,19 @@
       <c r="M14" s="3">
         <v>45960</v>
       </c>
-      <c r="N14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
         <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
       </c>
       <c r="E15" s="1">
         <v>4717</v>
@@ -1610,7 +1565,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2">
         <v>287476.15000000002</v>
@@ -1630,22 +1585,19 @@
       <c r="M15" s="3">
         <v>45960</v>
       </c>
-      <c r="N15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
       </c>
       <c r="E16" s="1">
         <v>5943</v>
@@ -1654,7 +1606,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2">
         <v>362194.35</v>
@@ -1674,22 +1626,19 @@
       <c r="M16" s="3">
         <v>45960</v>
       </c>
-      <c r="N16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
         <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
       </c>
       <c r="E17">
         <v>873</v>
@@ -1698,7 +1647,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2">
         <v>53204.72</v>
@@ -1718,22 +1667,19 @@
       <c r="M17" s="3">
         <v>45960</v>
       </c>
-      <c r="N17" t="s">
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
       <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
         <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
       </c>
       <c r="E18">
         <v>519</v>
@@ -1742,7 +1688,7 @@
         <v>60.944699999999997</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2">
         <v>31630.3</v>
@@ -1762,22 +1708,19 @@
       <c r="M18" s="3">
         <v>45960</v>
       </c>
-      <c r="N18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>9</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1">
         <v>1200</v>
@@ -1786,7 +1729,7 @@
         <v>44.499600000000001</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2">
         <v>53399.519999999997</v>
@@ -1805,9 +1748,6 @@
       </c>
       <c r="M19" s="3">
         <v>45960</v>
-      </c>
-      <c r="N19" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
